--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +1898,2482 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132618979</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>684130</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6555609</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132618991</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>684190</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6555759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132619000</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>683570</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6555663</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132618976</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>683598</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6555670</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132609062</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91949</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Näsudden, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>683671</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6555598</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132618997</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96328</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>683722</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6555737</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132618978</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>683955</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6555664</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132618975</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97963</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>683589</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6555670</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132618980</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>684156</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6555603</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132618986</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>684316</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6555729</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132618977</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>683855</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6555686</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132618994</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>683911</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6555750</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132609060</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Näsudden, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>684249</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6555778</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132609061</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96688</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Näsudden, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>683984</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6555810</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132609055</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Näsudden, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>684292</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6555735</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132618999</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>683612</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6555697</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132618990</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>684245</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6555779</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132618989</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>684242</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6555802</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132609058</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Näsudden, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>683638</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6555702</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132618995</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>683728</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6555713</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132618987</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>684293</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6555780</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132618988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Näsudden, Årsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>684280</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6555791</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -3490,48 +3490,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132609055</v>
+        <v>132618999</v>
       </c>
       <c r="B26" t="n">
-        <v>91892</v>
+        <v>101304</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684292</v>
+        <v>683612</v>
       </c>
       <c r="R26" t="n">
-        <v>6555735</v>
+        <v>6555697</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3558,9 +3558,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3575,19 +3585,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132618999</v>
+        <v>132618990</v>
       </c>
       <c r="B27" t="n">
         <v>101304</v>
@@ -3622,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>683612</v>
+        <v>684245</v>
       </c>
       <c r="R27" t="n">
-        <v>6555697</v>
+        <v>6555779</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3657,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3667,7 +3677,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3694,7 +3704,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132618990</v>
+        <v>132618989</v>
       </c>
       <c r="B28" t="n">
         <v>101304</v>
@@ -3729,10 +3739,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684245</v>
+        <v>684242</v>
       </c>
       <c r="R28" t="n">
-        <v>6555779</v>
+        <v>6555802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3764,7 +3774,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3784,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3801,48 +3811,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132618989</v>
+        <v>132609055</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>91892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684242</v>
+        <v>684292</v>
       </c>
       <c r="R29" t="n">
-        <v>6555802</v>
+        <v>6555735</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3869,19 +3879,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,12 +3896,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>132619000</v>
       </c>
       <c r="B14" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132618976</v>
       </c>
       <c r="B15" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>132609062</v>
       </c>
       <c r="B16" t="n">
-        <v>91949</v>
+        <v>91955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>132618997</v>
       </c>
       <c r="B17" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>132618978</v>
       </c>
       <c r="B18" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>132618975</v>
       </c>
       <c r="B19" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>132618980</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>132609060</v>
       </c>
       <c r="B24" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>132609061</v>
       </c>
       <c r="B25" t="n">
-        <v>96688</v>
+        <v>96696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>132618999</v>
       </c>
       <c r="B26" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>132618990</v>
       </c>
       <c r="B27" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>132618989</v>
       </c>
       <c r="B28" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>132609055</v>
       </c>
       <c r="B29" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>132618987</v>
       </c>
       <c r="B32" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2369,48 +2369,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132609062</v>
+        <v>132618978</v>
       </c>
       <c r="B16" t="n">
-        <v>91955</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683671</v>
+        <v>683955</v>
       </c>
       <c r="R16" t="n">
-        <v>6555598</v>
+        <v>6555664</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2437,40 +2442,49 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132618997</v>
+        <v>132618975</v>
       </c>
       <c r="B17" t="n">
-        <v>96336</v>
+        <v>97971</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,21 +2492,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2502,10 +2516,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683722</v>
+        <v>683589</v>
       </c>
       <c r="R17" t="n">
-        <v>6555737</v>
+        <v>6555670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2537,7 +2551,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2547,7 +2561,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,53 +2588,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132618978</v>
+        <v>132609062</v>
       </c>
       <c r="B18" t="n">
-        <v>57946</v>
+        <v>91955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683955</v>
+        <v>683671</v>
       </c>
       <c r="R18" t="n">
-        <v>6555664</v>
+        <v>6555598</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2647,49 +2656,40 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132618975</v>
+        <v>132618997</v>
       </c>
       <c r="B19" t="n">
-        <v>97971</v>
+        <v>96336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683589</v>
+        <v>683722</v>
       </c>
       <c r="R19" t="n">
-        <v>6555670</v>
+        <v>6555737</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>132619000</v>
       </c>
       <c r="B14" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132618976</v>
       </c>
       <c r="B15" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,50 +2369,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132618978</v>
+        <v>132618975</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>97981</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683955</v>
+        <v>683589</v>
       </c>
       <c r="R16" t="n">
-        <v>6555664</v>
+        <v>6555670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2444,7 +2439,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2454,7 +2449,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132618975</v>
+        <v>132609062</v>
       </c>
       <c r="B17" t="n">
-        <v>97971</v>
+        <v>91965</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,37 +2487,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683589</v>
+        <v>683671</v>
       </c>
       <c r="R17" t="n">
-        <v>6555670</v>
+        <v>6555598</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2549,49 +2544,40 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132609062</v>
+        <v>132618997</v>
       </c>
       <c r="B18" t="n">
-        <v>91955</v>
+        <v>96346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,37 +2585,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683671</v>
+        <v>683722</v>
       </c>
       <c r="R18" t="n">
-        <v>6555598</v>
+        <v>6555737</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2656,75 +2642,89 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132618997</v>
+        <v>132618978</v>
       </c>
       <c r="B19" t="n">
-        <v>96336</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683722</v>
+        <v>683955</v>
       </c>
       <c r="R19" t="n">
-        <v>6555737</v>
+        <v>6555664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,38 +2793,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132618980</v>
+        <v>132618986</v>
       </c>
       <c r="B20" t="n">
-        <v>57946</v>
+        <v>4781</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684156</v>
+        <v>684316</v>
       </c>
       <c r="R20" t="n">
-        <v>6555603</v>
+        <v>6555729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,6 +2889,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre levande gran</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2905,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618986</v>
+        <v>132618977</v>
       </c>
       <c r="B21" t="n">
-        <v>4781</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,27 +2936,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2945,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684316</v>
+        <v>683855</v>
       </c>
       <c r="R21" t="n">
-        <v>6555729</v>
+        <v>6555686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2980,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,22 +3024,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3037,38 +3052,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618977</v>
+        <v>132618980</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3077,10 +3092,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>683855</v>
+        <v>684156</v>
       </c>
       <c r="R22" t="n">
-        <v>6555686</v>
+        <v>6555603</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +3127,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,7 +3137,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,21 +3148,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>132609060</v>
       </c>
       <c r="B24" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>132609061</v>
       </c>
       <c r="B25" t="n">
-        <v>96696</v>
+        <v>96706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,48 +3490,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132618999</v>
+        <v>132609055</v>
       </c>
       <c r="B26" t="n">
-        <v>101312</v>
+        <v>91908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>683612</v>
+        <v>684292</v>
       </c>
       <c r="R26" t="n">
-        <v>6555697</v>
+        <v>6555735</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3558,19 +3558,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3585,22 +3575,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132618990</v>
+        <v>132618999</v>
       </c>
       <c r="B27" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3632,10 +3622,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684245</v>
+        <v>683612</v>
       </c>
       <c r="R27" t="n">
-        <v>6555779</v>
+        <v>6555697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3667,7 +3657,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,7 +3667,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3704,10 +3694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132618989</v>
+        <v>132618990</v>
       </c>
       <c r="B28" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,10 +3729,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684242</v>
+        <v>684245</v>
       </c>
       <c r="R28" t="n">
-        <v>6555802</v>
+        <v>6555779</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,7 +3764,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3784,7 +3774,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3811,48 +3801,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132609055</v>
+        <v>132618989</v>
       </c>
       <c r="B29" t="n">
-        <v>91898</v>
+        <v>101323</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684292</v>
+        <v>684242</v>
       </c>
       <c r="R29" t="n">
-        <v>6555735</v>
+        <v>6555802</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3879,9 +3869,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,12 +3896,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4132,38 +4132,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132618987</v>
+        <v>132618988</v>
       </c>
       <c r="B32" t="n">
-        <v>57946</v>
+        <v>4775</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684293</v>
+        <v>684280</v>
       </c>
       <c r="R32" t="n">
-        <v>6555780</v>
+        <v>6555791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,6 +4228,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4244,38 +4264,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132618988</v>
+        <v>132618987</v>
       </c>
       <c r="B33" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4284,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684280</v>
+        <v>684293</v>
       </c>
       <c r="R33" t="n">
-        <v>6555791</v>
+        <v>6555780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4329,7 +4349,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,26 +4360,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>132619000</v>
       </c>
       <c r="B14" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132618976</v>
       </c>
       <c r="B15" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132618975</v>
+        <v>132609062</v>
       </c>
       <c r="B16" t="n">
-        <v>97981</v>
+        <v>91966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,37 +2380,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683589</v>
+        <v>683671</v>
       </c>
       <c r="R16" t="n">
-        <v>6555670</v>
+        <v>6555598</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2437,49 +2437,40 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132609062</v>
+        <v>132618997</v>
       </c>
       <c r="B17" t="n">
-        <v>91965</v>
+        <v>96347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,37 +2478,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683671</v>
+        <v>683722</v>
       </c>
       <c r="R17" t="n">
-        <v>6555598</v>
+        <v>6555737</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,75 +2535,89 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132618997</v>
+        <v>132618978</v>
       </c>
       <c r="B18" t="n">
-        <v>96346</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683722</v>
+        <v>683955</v>
       </c>
       <c r="R18" t="n">
-        <v>6555737</v>
+        <v>6555664</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,7 +2649,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,7 +2659,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2681,50 +2686,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132618978</v>
+        <v>132618975</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>97982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683955</v>
+        <v>683589</v>
       </c>
       <c r="R19" t="n">
-        <v>6555664</v>
+        <v>6555670</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2925,38 +2925,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618977</v>
+        <v>132618980</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683855</v>
+        <v>684156</v>
       </c>
       <c r="R21" t="n">
-        <v>6555686</v>
+        <v>6555603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,21 +3021,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3052,38 +3037,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618980</v>
+        <v>132618977</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3092,10 +3077,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684156</v>
+        <v>683855</v>
       </c>
       <c r="R22" t="n">
-        <v>6555603</v>
+        <v>6555686</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3127,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3137,7 +3122,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3148,6 +3133,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>132609060</v>
       </c>
       <c r="B24" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>132609061</v>
       </c>
       <c r="B25" t="n">
-        <v>96706</v>
+        <v>96707</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>132609055</v>
       </c>
       <c r="B26" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>132618999</v>
       </c>
       <c r="B27" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>132618990</v>
       </c>
       <c r="B28" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>132618989</v>
       </c>
       <c r="B29" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>132619000</v>
       </c>
       <c r="B14" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132618976</v>
       </c>
       <c r="B15" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,48 +2369,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132609062</v>
+        <v>132618978</v>
       </c>
       <c r="B16" t="n">
-        <v>91966</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683671</v>
+        <v>683955</v>
       </c>
       <c r="R16" t="n">
-        <v>6555598</v>
+        <v>6555664</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2437,40 +2442,49 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132618997</v>
+        <v>132609062</v>
       </c>
       <c r="B17" t="n">
-        <v>96347</v>
+        <v>91966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,37 +2492,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>5321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683722</v>
+        <v>683671</v>
       </c>
       <c r="R17" t="n">
-        <v>6555737</v>
+        <v>6555598</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2535,89 +2549,75 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132618978</v>
+        <v>132618997</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>96348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683955</v>
+        <v>683722</v>
       </c>
       <c r="R18" t="n">
-        <v>6555664</v>
+        <v>6555737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,7 +2689,7 @@
         <v>132618975</v>
       </c>
       <c r="B19" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,38 +2793,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132618986</v>
+        <v>132618980</v>
       </c>
       <c r="B20" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684316</v>
+        <v>684156</v>
       </c>
       <c r="R20" t="n">
-        <v>6555729</v>
+        <v>6555603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,26 +2889,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Äldre levande gran</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre levande gran</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2925,38 +2905,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618980</v>
+        <v>132618977</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2965,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684156</v>
+        <v>683855</v>
       </c>
       <c r="R21" t="n">
-        <v>6555603</v>
+        <v>6555686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3000,7 +2980,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3010,7 +2990,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,6 +3001,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3037,10 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618977</v>
+        <v>132618986</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>4781</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,27 +3043,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>683855</v>
+        <v>684316</v>
       </c>
       <c r="R22" t="n">
-        <v>6555686</v>
+        <v>6555729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +3107,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,7 +3117,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,17 +3131,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Äldre levande gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
         <v>132609060</v>
       </c>
       <c r="B24" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>132609061</v>
       </c>
       <c r="B25" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>132618999</v>
       </c>
       <c r="B27" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>132618990</v>
       </c>
       <c r="B28" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>132618989</v>
       </c>
       <c r="B29" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4132,38 +4132,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132618988</v>
+        <v>132618987</v>
       </c>
       <c r="B32" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684280</v>
+        <v>684293</v>
       </c>
       <c r="R32" t="n">
-        <v>6555791</v>
+        <v>6555780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,26 +4228,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4264,38 +4244,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132618987</v>
+        <v>132618988</v>
       </c>
       <c r="B33" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4304,10 +4284,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684293</v>
+        <v>684280</v>
       </c>
       <c r="R33" t="n">
-        <v>6555780</v>
+        <v>6555791</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,7 +4319,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,7 +4329,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,6 +4340,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2905,10 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618977</v>
+        <v>132618986</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>4781</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,27 +2916,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683855</v>
+        <v>684316</v>
       </c>
       <c r="R21" t="n">
-        <v>6555686</v>
+        <v>6555729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,17 +3004,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Äldre levande gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3032,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618986</v>
+        <v>132618977</v>
       </c>
       <c r="B22" t="n">
-        <v>4781</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,27 +3048,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684316</v>
+        <v>683855</v>
       </c>
       <c r="R22" t="n">
-        <v>6555729</v>
+        <v>6555686</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3122,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,22 +3136,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>132619000</v>
       </c>
       <c r="B14" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>132618976</v>
       </c>
       <c r="B15" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2369,50 +2369,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132618978</v>
+        <v>132618975</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683955</v>
+        <v>683589</v>
       </c>
       <c r="R16" t="n">
-        <v>6555664</v>
+        <v>6555670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2444,7 +2439,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2454,7 +2449,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2686,45 +2681,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132618975</v>
+        <v>132618978</v>
       </c>
       <c r="B19" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683589</v>
+        <v>683955</v>
       </c>
       <c r="R19" t="n">
-        <v>6555670</v>
+        <v>6555664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,38 +2793,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132618980</v>
+        <v>132618986</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>4781</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684156</v>
+        <v>684316</v>
       </c>
       <c r="R20" t="n">
-        <v>6555603</v>
+        <v>6555729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,6 +2889,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre levande gran</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2905,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618986</v>
+        <v>132618977</v>
       </c>
       <c r="B21" t="n">
-        <v>4781</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,27 +2936,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2945,10 +2965,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684316</v>
+        <v>683855</v>
       </c>
       <c r="R21" t="n">
-        <v>6555729</v>
+        <v>6555686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2980,7 +3000,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +3010,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,22 +3024,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3037,38 +3052,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618977</v>
+        <v>132618980</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3077,10 +3092,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>683855</v>
+        <v>684156</v>
       </c>
       <c r="R22" t="n">
-        <v>6555686</v>
+        <v>6555603</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +3127,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,7 +3137,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,21 +3148,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3299,7 +3299,7 @@
         <v>132609060</v>
       </c>
       <c r="B24" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>132618999</v>
       </c>
       <c r="B27" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>132618990</v>
       </c>
       <c r="B28" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>132618989</v>
       </c>
       <c r="B29" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4132,38 +4132,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132618987</v>
+        <v>132618988</v>
       </c>
       <c r="B32" t="n">
-        <v>57950</v>
+        <v>4775</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684293</v>
+        <v>684280</v>
       </c>
       <c r="R32" t="n">
-        <v>6555780</v>
+        <v>6555791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,6 +4228,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4244,38 +4264,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132618988</v>
+        <v>132618987</v>
       </c>
       <c r="B33" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4284,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684280</v>
+        <v>684293</v>
       </c>
       <c r="R33" t="n">
-        <v>6555791</v>
+        <v>6555780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4329,7 +4349,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,26 +4360,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2369,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132618997</v>
+        <v>132618975</v>
       </c>
       <c r="B16" t="n">
-        <v>96358</v>
+        <v>97995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,21 +2380,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683722</v>
+        <v>683589</v>
       </c>
       <c r="R16" t="n">
-        <v>6555737</v>
+        <v>6555670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132609062</v>
+        <v>132618997</v>
       </c>
       <c r="B17" t="n">
-        <v>91975</v>
+        <v>96358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,37 +2487,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683671</v>
+        <v>683722</v>
       </c>
       <c r="R17" t="n">
-        <v>6555598</v>
+        <v>6555737</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,83 +2544,87 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132618978</v>
+        <v>132609062</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>91975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683955</v>
+        <v>683671</v>
       </c>
       <c r="R18" t="n">
-        <v>6555664</v>
+        <v>6555598</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2647,84 +2651,80 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132618975</v>
+        <v>132618978</v>
       </c>
       <c r="B19" t="n">
-        <v>97995</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683589</v>
+        <v>683955</v>
       </c>
       <c r="R19" t="n">
-        <v>6555670</v>
+        <v>6555664</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,38 +2793,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132618977</v>
+        <v>132618980</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683855</v>
+        <v>684156</v>
       </c>
       <c r="R20" t="n">
-        <v>6555686</v>
+        <v>6555603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,21 +2889,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2920,38 +2905,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618980</v>
+        <v>132618986</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>4781</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2960,10 +2945,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684156</v>
+        <v>684316</v>
       </c>
       <c r="R21" t="n">
-        <v>6555603</v>
+        <v>6555729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2995,7 +2980,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3005,7 +2990,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,6 +3001,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre levande gran</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3032,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618986</v>
+        <v>132618977</v>
       </c>
       <c r="B22" t="n">
-        <v>4781</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,27 +3048,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684316</v>
+        <v>683855</v>
       </c>
       <c r="R22" t="n">
-        <v>6555729</v>
+        <v>6555686</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3107,7 +3112,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3117,7 +3122,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,22 +3136,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3490,48 +3490,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132609055</v>
+        <v>132618999</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684292</v>
+        <v>683612</v>
       </c>
       <c r="R26" t="n">
-        <v>6555735</v>
+        <v>6555697</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3558,9 +3558,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3575,19 +3585,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132618989</v>
+        <v>132618990</v>
       </c>
       <c r="B27" t="n">
         <v>101338</v>
@@ -3622,10 +3632,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684242</v>
+        <v>684245</v>
       </c>
       <c r="R27" t="n">
-        <v>6555802</v>
+        <v>6555779</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3657,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3667,7 +3677,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3694,7 +3704,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132618999</v>
+        <v>132618989</v>
       </c>
       <c r="B28" t="n">
         <v>101338</v>
@@ -3729,10 +3739,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>683612</v>
+        <v>684242</v>
       </c>
       <c r="R28" t="n">
-        <v>6555697</v>
+        <v>6555802</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3764,7 +3774,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3784,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3801,48 +3811,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132618990</v>
+        <v>132609055</v>
       </c>
       <c r="B29" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684245</v>
+        <v>684292</v>
       </c>
       <c r="R29" t="n">
-        <v>6555779</v>
+        <v>6555735</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3869,19 +3879,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,12 +3896,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4132,38 +4132,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132618987</v>
+        <v>132618988</v>
       </c>
       <c r="B32" t="n">
-        <v>57955</v>
+        <v>4775</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684293</v>
+        <v>684280</v>
       </c>
       <c r="R32" t="n">
-        <v>6555780</v>
+        <v>6555791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,6 +4228,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4244,38 +4264,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132618988</v>
+        <v>132618987</v>
       </c>
       <c r="B33" t="n">
-        <v>4775</v>
+        <v>57955</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4284,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684280</v>
+        <v>684293</v>
       </c>
       <c r="R33" t="n">
-        <v>6555791</v>
+        <v>6555780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4329,7 +4349,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,26 +4360,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -2476,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132618997</v>
+        <v>132609062</v>
       </c>
       <c r="B17" t="n">
-        <v>96358</v>
+        <v>91975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,37 +2487,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>5321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683722</v>
+        <v>683671</v>
       </c>
       <c r="R17" t="n">
-        <v>6555737</v>
+        <v>6555598</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,49 +2544,40 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132609062</v>
+        <v>132618997</v>
       </c>
       <c r="B18" t="n">
-        <v>91975</v>
+        <v>96358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,37 +2585,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683671</v>
+        <v>683722</v>
       </c>
       <c r="R18" t="n">
-        <v>6555598</v>
+        <v>6555737</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2651,30 +2642,39 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3490,48 +3490,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132618999</v>
+        <v>132609055</v>
       </c>
       <c r="B26" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>683612</v>
+        <v>684292</v>
       </c>
       <c r="R26" t="n">
-        <v>6555697</v>
+        <v>6555735</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3558,19 +3558,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3585,19 +3575,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132618990</v>
+        <v>132618999</v>
       </c>
       <c r="B27" t="n">
         <v>101338</v>
@@ -3632,10 +3622,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684245</v>
+        <v>683612</v>
       </c>
       <c r="R27" t="n">
-        <v>6555779</v>
+        <v>6555697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3667,7 +3657,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,7 +3667,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3704,7 +3694,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132618989</v>
+        <v>132618990</v>
       </c>
       <c r="B28" t="n">
         <v>101338</v>
@@ -3739,10 +3729,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684242</v>
+        <v>684245</v>
       </c>
       <c r="R28" t="n">
-        <v>6555802</v>
+        <v>6555779</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,7 +3764,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3784,7 +3774,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3811,48 +3801,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132609055</v>
+        <v>132618989</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684292</v>
+        <v>684242</v>
       </c>
       <c r="R29" t="n">
-        <v>6555735</v>
+        <v>6555802</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3879,9 +3869,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,12 +3896,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89540921</v>
+        <v>104397650</v>
       </c>
       <c r="B2" t="n">
-        <v>95220</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2609</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -719,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683616.9930705719</v>
+        <v>684195</v>
       </c>
       <c r="R2" t="n">
-        <v>6555710.149813144</v>
+        <v>6555490</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6 gamla och 6 nya kapslar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89540788</v>
+        <v>104397820</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,26 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -836,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683616.9930705719</v>
+        <v>684247</v>
       </c>
       <c r="R3" t="n">
-        <v>6555710.149813144</v>
+        <v>6555774</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +867,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nya för året.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,58 +893,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104362812</v>
+        <v>104397850</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -957,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684221.2862081991</v>
+        <v>684359</v>
       </c>
       <c r="R4" t="n">
-        <v>6555502.057568093</v>
+        <v>6555753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,27 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 80+40 med några meters avstånd.</t>
+          <t>Från förra året.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,57 +1020,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104397335</v>
+        <v>132609055</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683895.4353354031</v>
+        <v>684292</v>
       </c>
       <c r="R5" t="n">
-        <v>6555643.283170494</v>
+        <v>6555735</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,34 +1099,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104397820</v>
+        <v>132609061</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,49 +1128,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684246.8067524042</v>
+        <v>683984</v>
       </c>
       <c r="R6" t="n">
-        <v>6555774.430977815</v>
+        <v>6555810</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,27 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Nya för året.</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,61 +1196,56 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104397316</v>
+        <v>89540921</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2609</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1325,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684113.6970756151</v>
+        <v>683617</v>
       </c>
       <c r="R7" t="n">
-        <v>6555477.833759841</v>
+        <v>6555710</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,27 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På grenar på levande gran.</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,27 +1304,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104397850</v>
+        <v>89540788</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,34 +1327,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>2779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1455,13 +1355,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684359.1873320279</v>
+        <v>683617</v>
       </c>
       <c r="R8" t="n">
-        <v>6555752.585219377</v>
+        <v>6555710</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,27 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Från förra året.</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,65 +1406,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104397884</v>
+        <v>132618997</v>
       </c>
       <c r="B9" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683650.5673101237</v>
+        <v>683722</v>
       </c>
       <c r="R9" t="n">
-        <v>6555569.249209145</v>
+        <v>6555737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,22 +1483,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,34 +1507,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104397650</v>
+        <v>132609062</v>
       </c>
       <c r="B10" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,49 +1536,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>5321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684194.5512823358</v>
+        <v>683671</v>
       </c>
       <c r="R10" t="n">
-        <v>6555489.963540453</v>
+        <v>6555598</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,27 +1590,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>6 gamla och 6 nya kapslar.</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,27 +1611,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104397517</v>
+        <v>104397884</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684180.4688066191</v>
+        <v>683651</v>
       </c>
       <c r="R11" t="n">
-        <v>6555493.400762319</v>
+        <v>6555569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1855,24 +1694,9 @@
           <t>2022-10-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grenar på en ganska grov, levande gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132618979</v>
+        <v>132609059</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>75354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,42 +1735,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6427</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684130</v>
+        <v>683720</v>
       </c>
       <c r="R12" t="n">
-        <v>6555609</v>
+        <v>6555653</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1973,65 +1792,39 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132618991</v>
+        <v>132609057</v>
       </c>
       <c r="B13" t="n">
-        <v>8444</v>
+        <v>81031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,42 +1832,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6444</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skriftlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Graphis scripta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684190</v>
+        <v>683720</v>
       </c>
       <c r="R13" t="n">
-        <v>6555759</v>
+        <v>6555652</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2101,21 +1889,11 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2124,41 +1902,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132619000</v>
+        <v>132618978</v>
       </c>
       <c r="B14" t="n">
-        <v>101338</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,34 +1929,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683570</v>
+        <v>683955</v>
       </c>
       <c r="R14" t="n">
-        <v>6555663</v>
+        <v>6555664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2225,7 +1993,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2235,7 +2003,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2262,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132618976</v>
+        <v>132618980</v>
       </c>
       <c r="B15" t="n">
-        <v>101338</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,34 +2041,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683598</v>
+        <v>684156</v>
       </c>
       <c r="R15" t="n">
-        <v>6555670</v>
+        <v>6555603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2332,7 +2105,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2115,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132618975</v>
+        <v>132618987</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,34 +2153,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683589</v>
+        <v>684293</v>
       </c>
       <c r="R16" t="n">
-        <v>6555670</v>
+        <v>6555780</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,7 +2217,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2449,7 +2227,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2476,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132609062</v>
+        <v>132618988</v>
       </c>
       <c r="B17" t="n">
-        <v>91975</v>
+        <v>4776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,37 +2265,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683671</v>
+        <v>684280</v>
       </c>
       <c r="R17" t="n">
-        <v>6555598</v>
+        <v>6555791</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2544,40 +2327,69 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132618997</v>
+        <v>132618994</v>
       </c>
       <c r="B18" t="n">
-        <v>96358</v>
+        <v>4776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,34 +2397,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683722</v>
+        <v>683911</v>
       </c>
       <c r="R18" t="n">
-        <v>6555737</v>
+        <v>6555750</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2644,7 +2461,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,7 +2471,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2665,6 +2482,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2681,38 +2518,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132618978</v>
+        <v>132618986</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>4782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2721,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683955</v>
+        <v>684316</v>
       </c>
       <c r="R19" t="n">
-        <v>6555664</v>
+        <v>6555729</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2603,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,6 +2614,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre levande gran</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2793,53 +2650,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132618980</v>
+        <v>132609058</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>8460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684156</v>
+        <v>683638</v>
       </c>
       <c r="R20" t="n">
-        <v>6555603</v>
+        <v>6555702</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2866,19 +2718,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2893,22 +2735,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132618986</v>
+        <v>132618977</v>
       </c>
       <c r="B21" t="n">
-        <v>4781</v>
+        <v>8460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,27 +2758,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2945,10 +2787,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684316</v>
+        <v>683855</v>
       </c>
       <c r="R21" t="n">
-        <v>6555729</v>
+        <v>6555686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2980,7 +2822,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +2832,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,22 +2846,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre levande gran</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3037,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132618977</v>
+        <v>132618979</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3068,7 +2905,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3077,10 +2914,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>683855</v>
+        <v>684130</v>
       </c>
       <c r="R22" t="n">
-        <v>6555686</v>
+        <v>6555609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,7 +2949,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3122,7 +2959,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,6 +2968,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3164,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132618994</v>
+        <v>132618995</v>
       </c>
       <c r="B23" t="n">
-        <v>4775</v>
+        <v>8460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3175,21 +3013,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3204,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>683911</v>
+        <v>683728</v>
       </c>
       <c r="R23" t="n">
-        <v>6555750</v>
+        <v>6555713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3239,7 +3077,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3249,7 +3087,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3263,22 +3101,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3296,10 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132609060</v>
+        <v>132618991</v>
       </c>
       <c r="B24" t="n">
-        <v>101338</v>
+        <v>8449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3307,37 +3140,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684249</v>
+        <v>684190</v>
       </c>
       <c r="R24" t="n">
-        <v>6555778</v>
+        <v>6555759</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3364,11 +3202,21 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3377,64 +3225,87 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132609061</v>
+        <v>104362812</v>
       </c>
       <c r="B25" t="n">
-        <v>96718</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>683984</v>
+        <v>684221</v>
       </c>
       <c r="R25" t="n">
-        <v>6555810</v>
+        <v>6555502</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3458,12 +3329,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2022-10-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2022-10-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ca. 80+40 med några meters avstånd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,66 +3348,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132609055</v>
+        <v>104397335</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>106244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684292</v>
+        <v>683895</v>
       </c>
       <c r="R26" t="n">
-        <v>6555735</v>
+        <v>6555643</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3555,12 +3436,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,28 +3450,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132618999</v>
+        <v>132618975</v>
       </c>
       <c r="B27" t="n">
-        <v>101338</v>
+        <v>98060</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,21 +3480,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3622,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>683612</v>
+        <v>683589</v>
       </c>
       <c r="R27" t="n">
-        <v>6555697</v>
+        <v>6555670</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3657,7 +3539,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3667,7 +3549,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3694,10 +3576,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132618990</v>
+        <v>132609060</v>
       </c>
       <c r="B28" t="n">
-        <v>101338</v>
+        <v>101403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,17 +3607,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Näsudden, Årsta, Srm</t>
+          <t>Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684245</v>
+        <v>684249</v>
       </c>
       <c r="R28" t="n">
-        <v>6555779</v>
+        <v>6555778</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3762,19 +3644,9 @@
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,22 +3661,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132618989</v>
+        <v>132618976</v>
       </c>
       <c r="B29" t="n">
-        <v>101338</v>
+        <v>101403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684242</v>
+        <v>683598</v>
       </c>
       <c r="R29" t="n">
-        <v>6555802</v>
+        <v>6555670</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3871,7 +3743,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,7 +3753,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,10 +3780,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132609058</v>
+        <v>132618989</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>101403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,37 +3791,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Näsudden, Srm</t>
+          <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>683638</v>
+        <v>684242</v>
       </c>
       <c r="R30" t="n">
-        <v>6555702</v>
+        <v>6555802</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3976,9 +3848,19 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3993,22 +3875,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Jörgen Sundin, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132618995</v>
+        <v>132618990</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>101403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4016,39 +3898,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>683728</v>
+        <v>684245</v>
       </c>
       <c r="R31" t="n">
-        <v>6555713</v>
+        <v>6555779</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4080,7 +3957,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4090,7 +3967,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4101,21 +3978,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4132,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132618988</v>
+        <v>132618999</v>
       </c>
       <c r="B32" t="n">
-        <v>4775</v>
+        <v>101403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,39 +4005,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100299</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>684280</v>
+        <v>683612</v>
       </c>
       <c r="R32" t="n">
-        <v>6555791</v>
+        <v>6555697</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,7 +4064,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4217,7 +4074,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,26 +4085,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4264,50 +4101,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132618987</v>
+        <v>132619000</v>
       </c>
       <c r="B33" t="n">
-        <v>57955</v>
+        <v>101403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Näsudden, Årsta, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684293</v>
+        <v>683570</v>
       </c>
       <c r="R33" t="n">
-        <v>6555780</v>
+        <v>6555663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,7 +4171,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,7 +4181,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 17454-2026 artfynd.xlsx
+++ b/artfynd/A 17454-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104397650</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104397820</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104397850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609055</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609061</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89540921</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89540788</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618997</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609062</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1721,6 +1771,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104397884</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609059</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609057</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618978</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2139,6 +2209,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618980</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618987</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2383,6 +2463,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618988</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618994</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2647,6 +2737,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618986</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2744,6 +2839,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609058</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2871,6 +2971,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618977</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2999,6 +3104,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618979</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3126,6 +3236,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618995</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3253,6 +3368,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618991</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3364,6 +3484,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104362812</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3466,6 +3591,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104397335</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3703,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618975</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3670,6 +3805,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132609060</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3777,6 +3917,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618976</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3884,6 +4029,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618989</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3991,6 +4141,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618990</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4098,6 +4253,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132618999</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4205,8 +4365,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132619000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>